--- a/4_четверть_28_TypeScript.xlsx
+++ b/4_четверть_28_TypeScript.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35253E1-6093-43DA-B49C-3E2788751C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2F0237-6E9B-49FA-AC90-C2C0284D24F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="-16575" windowWidth="26445" windowHeight="13470" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7635" yWindow="-18330" windowWidth="23250" windowHeight="12450" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Установка Компиляция" sheetId="12" r:id="rId1"/>
-    <sheet name="Типизация" sheetId="13" r:id="rId2"/>
+    <sheet name="Типы данных" sheetId="13" r:id="rId2"/>
+    <sheet name="Функции" sheetId="14" r:id="rId3"/>
+    <sheet name="Объединение типов" sheetId="15" r:id="rId4"/>
+    <sheet name="null undefined" sheetId="16" r:id="rId5"/>
+    <sheet name="Objects" sheetId="17" r:id="rId6"/>
+    <sheet name="type aliases" sheetId="18" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="178">
   <si>
     <t>Установка</t>
   </si>
@@ -463,9 +468,6 @@
       </rPr>
       <t>, можно воспользоваться параметром -h</t>
     </r>
-  </si>
-  <si>
-    <t>Файл конфигурации tsconfig.json</t>
   </si>
   <si>
     <t>Ссылка</t>
@@ -1982,17 +1984,6 @@
   </si>
   <si>
     <t>Оператор typeof может возвращать следующие значения</t>
-  </si>
-  <si>
-    <t>let sum: any;
-sum = 1200;
-if (typeof sum === "number") { 
-    let result: number = sum / 12;
-    console.log(result);
-}
-else{
-    console.log("invalid operation");
-}</t>
   </si>
   <si>
     <t>function</t>
@@ -2433,12 +2424,1678 @@
       <t>Необязательные параметры должны быть помечены вопросительным знаком ?.</t>
     </r>
   </si>
+  <si>
+    <t>При присвоении функции другой переменной</t>
+  </si>
+  <si>
+    <r>
+      <t>function sum (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x: number, y: number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+    return x + y;
+};
+function subtract (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a: number, b: number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+    return a - b;
+};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>let op: (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x:number, y:number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=&gt; number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;
+op = sum;
+console.log(op(2, 4));  // 6
+op = subtract;
+console.log(op(6, 4));  // 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Присвоение функции другой переменной</t>
+    </r>
+  </si>
+  <si>
+    <t>Функции как параметры других функций</t>
+  </si>
+  <si>
+    <t>function sum (x: number, y: number): number {
+    return x + y;
+};
+function multiply (a: number, b: number): number {
+    return a * b;
+};</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">function mathOp(x: number, y: number, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>op: (a: number, b: number) =&gt; number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">): number{
+    return op(x, y);
+}
+console.log(mathOp(10, 20, sum)); // 30 
+console.log(mathOp(10, 20, multiply)); // 200 </t>
+    </r>
+  </si>
+  <si>
+    <t>Стрелочные функции</t>
+  </si>
+  <si>
+    <r>
+      <t>const sum = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x: number, y: number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) =&gt; x + y;
+const result = sum(15, 35); // 50
+console.log(result);</t>
+    </r>
+  </si>
+  <si>
+    <t>union</t>
+  </si>
+  <si>
+    <t>C помощью объединений можно определить переменную, которая может хранить значение двух или более типов</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let id : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>number | string;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+id = "1345dgg5";
+console.log(id); // 1345dgg5
+id = 234;
+console.log(id);  // 234</t>
+    </r>
+  </si>
+  <si>
+    <t>Переменная</t>
+  </si>
+  <si>
+    <t>Функция</t>
+  </si>
+  <si>
+    <r>
+      <t>function printId(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>id: number|string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>){
+    console.log(`Id: ${id}`);
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">function printSentence(words: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>string[]|string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>){
+      // если words - строка
+      if (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>typeof words === "string"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) {
+        console.log(words);
+      } else {
+        // Если words - массив string[]
+        console.log(words.join(" "));
+      }
+}
+printSentence(["Язык", "программирования", "TypeScript"]);
+printSentence("Язык программирования JavaScript");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Практический пример
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> иногда </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>логика может различаться в зависимости от переданного типа</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. В этом случае можно использовать проверку на тип, чтобы разграничить логику для различных типов</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Файл конфигурации</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tsconfig.json</t>
+    </r>
+  </si>
+  <si>
+    <t>tsconfig.json</t>
+  </si>
+  <si>
+    <t>tsc app.ts --strictNullChecks true</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tsc app.ts </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--strictNullChecks true</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">по умолчанию мы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не можем применять типы undefined и null</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>let sum: any;
+sum = 1200;
+if (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>typeof sum === "number"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) { 
+    let result: number = sum / 12;
+    console.log(result);
+}
+else{
+    console.log("invalid operation");
+}</t>
+    </r>
+  </si>
+  <si>
+    <t>Типы undefined и null</t>
+  </si>
+  <si>
+    <t>let x: number = undefined;
+console.log(x);
+x = null;
+console.log(x);
+x = 5;
+console.log(x);</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{
+  "compilerOptions": {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    "strictNullChecks": true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Возможно, если:
+ИЛИ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tsc app.ts --strictNullChecks false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ИЛИ {
+  "compilerOptions": {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    "strictNullChecks": false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  }
+}
+В этом плане </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>null и undefined</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> выступают как подтипы других типов и полезны преимущественно в каких-то операциях, где неизвестен результат - то ли это будет число или строка, то ли это будет null</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Возможно, если:
+ИЛИ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tsc app.ts --strictNullChecks true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ИЛИ {
+  "compilerOptions": {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"strictNullChecks": true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let userId: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>number|null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = null;
+function printId(id: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>number|null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>){
+    if (id === null) {
+        console.log("пользователь отсутствует");
+    } else {
+        console.log(`id пользователя: ${id}`);
+    }
+}
+printId(userId)     // пользователь отсутствует
+userId = 45;
+printId(userId);    // id пользователя: 45</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>let</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a: undefined = undefined;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+let</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b: null = null;</t>
+    </r>
+  </si>
+  <si>
+    <t>tsc app.ts --strictNullChecks false</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const header: HTMLElement|null = document.getElementById("header");
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>header.innerText</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = "Hello Typescript!";</t>
+    </r>
+  </si>
+  <si>
+    <t>const header: HTMLElement|null = document.getElementById("header");
+header!.innerText = "Hello Typescript!";</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">С включенной опцией strictNullChecks при компиляции </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>мы получим ошибку</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Чтобы избежать ошибки</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, используем оператор !</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>! — это «обман»</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> только для проверки типов, не защита от реального null.</t>
+    </r>
+  </si>
+  <si>
+    <t>Оператор !</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let person = { name: "Tom", age: 23 };
+person = { name: "Bob" };           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>// ! Ошибка</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let person = { name: "Tom", age: 23 };
+person = { name: "Bob", age: 35 };      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>// Норм</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Компилятор после первой строки предполагает, что объект person будет иметь два свойства name и age, которые имеют тип string и number соответственно. </t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>person: { name: string; age: number }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = { name: "Tom", age: 23 };
+console.log(person.name);</t>
+    </r>
+  </si>
+  <si>
+    <t>Необязательные свойства</t>
+  </si>
+  <si>
+    <t>Объекты</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/web/typescript/2.7.php</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>person: { name: string; age?: number };</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // Свойство age - необязательное
+person = { name: "Tom", age: 23 };
+console.log(person.name);   // Tom
+person =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> { name: "Bob"};   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // Норм, свойство age - необязательное
+console.log(person.name);   // Bob</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">function </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(x: number, y: number): number</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{
+    return x + y;
+};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>let op: (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x:number, y:number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=&gt; number = sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;
+op = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;
+console.log(op(2, 4));  // 6
+op = subtract;
+console.log(op(6, 4));  // 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>function printUser(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user: { name: string; age: number}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) {
+  console.log(`name: ${user.name}  age: ${user.age}`);
+}
+let tom = {age: 36, name: "Tom"};
+printUser(tom);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Если объект очень большой!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> При этом объект, передаваемый в качестве параметра, может быть более широким - содержать больше свойств, но главное, чтобы он содержал те свойства, которые предусмотрены для параметра функции</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>function printUser(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user: { name: string; age: number}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) {
+  console.log(`name: ${user.name}  age: ${user.age}`);
+}
+let bob = {name: "Bob", age: 44, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isMarried: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>};
+printUser(bob);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>function defaultUser()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: { name: string; age: number}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+  return {name: "Tom", age: 37};
+}
+let user = defaultUser();
+console.log(`name: ${user.name}  age: ${user.age}`);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Функции: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Декомпозиция объектов-параметров</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Функции: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>объекты возвращаются</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Функции: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>объекты в параметрах</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>function printUser(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{name, age}: { name: string; age: number}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) {
+  console.log(`name: ${name}  age: ${age}`);
+}
+let tom = {name: "Tom", age: 36};
+printUser(tom);</t>
+    </r>
+  </si>
+  <si>
+    <t>Здесь функция printUser() в качестве параметра принимает объект из двух свойств. Запись {name, age} указывает, что свойства объекта автоматически будут разложены на два параметра: name и age. Главное, чтобы названия этих параметров соответствовали названиям свойств объекта.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">function printUser({name, age}: { name: string; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>age?: number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}) {
+  if(age!==undefined){ console.log(`name: ${name}  age: ${age}`);}
+  else {console.log(`name: ${name}`);}
+}
+let tom = {name: "Tom"};
+printUser(tom);     // name: Tom
+let bob = {name: "Bob", age: 44};
+printUser(bob);     // name: Bob  age: 44</t>
+    </r>
+  </si>
+  <si>
+    <t>Некоторые параметры могут необязательными</t>
+  </si>
+  <si>
+    <t>Могут принимать значения по умолчанию</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">function printUser({name, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>age = 25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}: { name: string; age?: number}) {
+  console.log(`name: ${name}  age: ${age}`);
+}
+let tom = {name: "Tom"};
+printUser(tom);     // name: Tom  age: 25
+let bob = {name: "Bob", age: 44};
+printUser(bob);     // name: Bob  age: 44</t>
+    </r>
+  </si>
+  <si>
+    <t>type aliases</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/web/typescript/2.14.php</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">позволяет определять псевдонимы типов с помощью ключевого слова </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> id =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> number | string;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+let userId : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 2;
+console.log(`Id: ${userId}`);
+userId = "qwerty";
+console.log(`Id: ${userId}`);</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2599,6 +4256,22 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2669,7 +4342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2742,6 +4415,25 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2765,14 +4457,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:colOff>64769</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3755975</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>796709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2796,8 +4488,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10887074" y="6627495"/>
-          <a:ext cx="3696921" cy="712889"/>
+          <a:off x="10885169" y="7715250"/>
+          <a:ext cx="3687396" cy="710984"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3076,7 +4768,7 @@
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -3110,10 +4802,10 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C1" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -3124,7 +4816,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C4" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -3245,7 +4937,7 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -3274,182 +4966,204 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C26" s="10" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C28" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C29" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C30" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="U31" s="5"/>
-    </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C32" s="9" t="s">
+      <c r="A32" s="3"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="U32" s="5"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C33" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="13" t="s">
+    </row>
+    <row r="34" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B33" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>39</v>
+      <c r="D34" s="15"/>
+      <c r="E34" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
+        <v>50</v>
+      </c>
       <c r="B35" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="2" t="s">
+    </row>
+    <row r="36" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B36" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
+      <c r="C37" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="72" x14ac:dyDescent="0.3">
+      <c r="A38" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C39" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="U41" s="5"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C42" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C44" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C37" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="U39" s="5"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C40" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C42" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="17" t="s">
+      <c r="D45" s="10" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D32" r:id="rId1" xr:uid="{813E5610-7243-4D46-8DE5-030FFA9D524A}"/>
-    <hyperlink ref="D40" r:id="rId2" xr:uid="{D40342D1-7AE8-47E2-BF98-979FFBC1804F}"/>
+    <hyperlink ref="D33" r:id="rId1" xr:uid="{813E5610-7243-4D46-8DE5-030FFA9D524A}"/>
+    <hyperlink ref="D42" r:id="rId2" xr:uid="{D40342D1-7AE8-47E2-BF98-979FFBC1804F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
@@ -3460,9 +5174,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57BF7846-A236-4D8E-A4FF-ADEBE704C817}">
   <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -3505,7 +5220,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C4" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -3538,10 +5253,10 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C9" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P9" s="1"/>
       <c r="U9" s="1"/>
@@ -3549,176 +5264,176 @@
     </row>
     <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C13" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C15" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C16" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C17" s="22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C18" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C19" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="C20" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C28" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>81</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
@@ -3742,10 +5457,10 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C39" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P39" s="1"/>
       <c r="U39" s="1"/>
@@ -3753,18 +5468,18 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
@@ -3788,81 +5503,858 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C44" s="21" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="2"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A45" s="17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>102</v>
+    <row r="45" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C45" s="25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="29" t="s">
+        <v>144</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>103</v>
+        <v>140</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="20" t="s">
+        <v>133</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>104</v>
+        <v>141</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
-        <v>108</v>
+      <c r="A48" s="20" t="s">
+        <v>133</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C53" s="25"/>
+        <v>147</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B49" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D9" r:id="rId1" xr:uid="{06CC6BA1-50B0-4E53-92BD-0A855505505F}"/>
     <hyperlink ref="D39" r:id="rId2" location=":~:text=%D0%9F%D1%80%D0%BE%D0%B2%D0%B5%D1%80%D0%BA%D0%B0%20%D1%82%D0%B8%D0%BF%D0%B0" xr:uid="{DD45ABB3-3F50-480C-BC3E-6E8DEE6B0A98}"/>
-    <hyperlink ref="D44" r:id="rId3" xr:uid="{956962A2-D847-4BB8-93DF-26C272B75A01}"/>
+    <hyperlink ref="D44" r:id="rId3" xr:uid="{56969F60-9E71-4878-AA41-EEC8527D7BF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D858FB-D6DE-4F73-98BB-B40AAF0AFFB1}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V24"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C4" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C9" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C18" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C21" s="25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C24" s="25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{9AE3E42A-082A-4A49-A85E-1E90E22B3A9F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8208F76-FF4B-4C3B-85A6-4387A14D0E90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C4" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C9" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C10" s="25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{008C93CE-4062-4825-B784-9EAD35FB9146}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8DB89A9-F93E-472C-823E-B1FD6A4FA7A8}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C4" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C9" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C10" s="25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B14" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{95B0EC02-3FA0-404A-A8EF-E6341E121CCB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D92B39-09D9-46F9-9173-2B9A9B0CEF26}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="31"/>
+      <c r="C9" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="31"/>
+    </row>
+    <row r="10" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C12" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="25"/>
+    </row>
+    <row r="14" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C14" s="25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+      <c r="C16" s="25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="B17" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C19" s="25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="25"/>
+      <c r="B21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A4D51A-E79B-4039-970D-1EA14C733F5D}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:U10"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="31"/>
+      <c r="C9" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="31"/>
+    </row>
+    <row r="10" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>